--- a/data/stx_xlsx/NELLY.ST.xlsx
+++ b/data/stx_xlsx/NELLY.ST.xlsx
@@ -11654,12 +11654,21 @@
       <c r="P70" s="15">
         <v>499.11</v>
       </c>
-      <c r="Q70" s="18"/>
-      <c r="R70" s="18"/>
+      <c r="Q70" s="19">
+        <f t="shared" ref="Q70:R70" si="1">SUM(Q79:Q80)</f>
+        <v>3.18</v>
+      </c>
+      <c r="R70" s="19">
+        <f t="shared" si="1"/>
+        <v>1.58</v>
+      </c>
       <c r="S70" s="19">
         <v>4.77</v>
       </c>
-      <c r="T70" s="18"/>
+      <c r="T70" s="19">
+        <f>SUM(T79:T80)</f>
+        <v>1.24</v>
+      </c>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
